--- a/data.mn/public/datasets/mrpam-fuel-prices.xlsx
+++ b/data.mn/public/datasets/mrpam-fuel-prices.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DG67"/>
+  <dimension ref="A1:DG69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -16951,6 +16951,642 @@
         <v>5000</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>3160</v>
+      </c>
+      <c r="C68" t="n">
+        <v>5480</v>
+      </c>
+      <c r="D68" t="n">
+        <v>5530</v>
+      </c>
+      <c r="E68" t="n">
+        <v>5020</v>
+      </c>
+      <c r="F68" t="n">
+        <v>5170</v>
+      </c>
+      <c r="G68" t="n">
+        <v>3610</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="n">
+        <v>5990</v>
+      </c>
+      <c r="J68" t="n">
+        <v>5250</v>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="n">
+        <v>3190</v>
+      </c>
+      <c r="M68" t="n">
+        <v>5510</v>
+      </c>
+      <c r="N68" t="n">
+        <v>5560</v>
+      </c>
+      <c r="O68" t="n">
+        <v>5090</v>
+      </c>
+      <c r="P68" t="n">
+        <v>5240</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>3180</v>
+      </c>
+      <c r="R68" t="n">
+        <v>5500</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5550</v>
+      </c>
+      <c r="T68" t="n">
+        <v>5030</v>
+      </c>
+      <c r="U68" t="n">
+        <v>5180</v>
+      </c>
+      <c r="V68" t="n">
+        <v>3130</v>
+      </c>
+      <c r="W68" t="n">
+        <v>5450</v>
+      </c>
+      <c r="X68" t="n">
+        <v>5500</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>5000</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>5150</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>3190</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>5540</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>5590</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>4900</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>5150</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>3180</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>5560</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>5550</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>5070</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>5220</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>3290</v>
+      </c>
+      <c r="AL68" t="inlineStr"/>
+      <c r="AM68" t="n">
+        <v>5610</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>5050</v>
+      </c>
+      <c r="AO68" t="inlineStr"/>
+      <c r="AP68" t="n">
+        <v>3460</v>
+      </c>
+      <c r="AQ68" t="inlineStr"/>
+      <c r="AR68" t="n">
+        <v>5850</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>5450</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>5550</v>
+      </c>
+      <c r="AU68" t="n">
+        <v>3140</v>
+      </c>
+      <c r="AV68" t="n">
+        <v>5560</v>
+      </c>
+      <c r="AW68" t="n">
+        <v>5610</v>
+      </c>
+      <c r="AX68" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AY68" t="n">
+        <v>5100</v>
+      </c>
+      <c r="AZ68" t="n">
+        <v>3210</v>
+      </c>
+      <c r="BA68" t="n">
+        <v>5500</v>
+      </c>
+      <c r="BB68" t="n">
+        <v>5550</v>
+      </c>
+      <c r="BC68" t="n">
+        <v>5000</v>
+      </c>
+      <c r="BD68" t="n">
+        <v>5200</v>
+      </c>
+      <c r="BE68" t="n">
+        <v>3610</v>
+      </c>
+      <c r="BF68" t="inlineStr"/>
+      <c r="BG68" t="n">
+        <v>5900</v>
+      </c>
+      <c r="BH68" t="n">
+        <v>5350</v>
+      </c>
+      <c r="BI68" t="n">
+        <v>5450</v>
+      </c>
+      <c r="BJ68" t="n">
+        <v>3250</v>
+      </c>
+      <c r="BK68" t="n">
+        <v>5570</v>
+      </c>
+      <c r="BL68" t="n">
+        <v>5620</v>
+      </c>
+      <c r="BM68" t="n">
+        <v>5070</v>
+      </c>
+      <c r="BN68" t="n">
+        <v>5170</v>
+      </c>
+      <c r="BO68" t="n">
+        <v>3150</v>
+      </c>
+      <c r="BP68" t="n">
+        <v>5470</v>
+      </c>
+      <c r="BQ68" t="n">
+        <v>5520</v>
+      </c>
+      <c r="BR68" t="n">
+        <v>5000</v>
+      </c>
+      <c r="BS68" t="n">
+        <v>5150</v>
+      </c>
+      <c r="BT68" t="n">
+        <v>3250</v>
+      </c>
+      <c r="BU68" t="n">
+        <v>5570</v>
+      </c>
+      <c r="BV68" t="n">
+        <v>5540</v>
+      </c>
+      <c r="BW68" t="n">
+        <v>5030</v>
+      </c>
+      <c r="BX68" t="n">
+        <v>5180</v>
+      </c>
+      <c r="BY68" t="n">
+        <v>3230</v>
+      </c>
+      <c r="BZ68" t="inlineStr"/>
+      <c r="CA68" t="n">
+        <v>5610</v>
+      </c>
+      <c r="CB68" t="n">
+        <v>5020</v>
+      </c>
+      <c r="CC68" t="n">
+        <v>5270</v>
+      </c>
+      <c r="CD68" t="n">
+        <v>3160</v>
+      </c>
+      <c r="CE68" t="n">
+        <v>5500</v>
+      </c>
+      <c r="CF68" t="inlineStr"/>
+      <c r="CG68" t="n">
+        <v>5000</v>
+      </c>
+      <c r="CH68" t="inlineStr"/>
+      <c r="CI68" t="n">
+        <v>3040</v>
+      </c>
+      <c r="CJ68" t="n">
+        <v>4960</v>
+      </c>
+      <c r="CK68" t="n">
+        <v>4990</v>
+      </c>
+      <c r="CL68" t="n">
+        <v>4190</v>
+      </c>
+      <c r="CM68" t="n">
+        <v>4940</v>
+      </c>
+      <c r="CN68" t="n">
+        <v>3210</v>
+      </c>
+      <c r="CO68" t="n">
+        <v>5530</v>
+      </c>
+      <c r="CP68" t="n">
+        <v>5580</v>
+      </c>
+      <c r="CQ68" t="n">
+        <v>5000</v>
+      </c>
+      <c r="CR68" t="n">
+        <v>5100</v>
+      </c>
+      <c r="CS68" t="n">
+        <v>3560</v>
+      </c>
+      <c r="CT68" t="inlineStr"/>
+      <c r="CU68" t="n">
+        <v>5990</v>
+      </c>
+      <c r="CV68" t="n">
+        <v>5500</v>
+      </c>
+      <c r="CW68" t="n">
+        <v>5600</v>
+      </c>
+      <c r="CX68" t="n">
+        <v>3190</v>
+      </c>
+      <c r="CY68" t="n">
+        <v>5450</v>
+      </c>
+      <c r="CZ68" t="n">
+        <v>5500</v>
+      </c>
+      <c r="DA68" t="n">
+        <v>5010</v>
+      </c>
+      <c r="DB68" t="n">
+        <v>5160</v>
+      </c>
+      <c r="DC68" t="n">
+        <v>3460</v>
+      </c>
+      <c r="DD68" t="n">
+        <v>5870</v>
+      </c>
+      <c r="DE68" t="n">
+        <v>5920</v>
+      </c>
+      <c r="DF68" t="n">
+        <v>5600</v>
+      </c>
+      <c r="DG68" t="n">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>3160</v>
+      </c>
+      <c r="C69" t="n">
+        <v>5480</v>
+      </c>
+      <c r="D69" t="n">
+        <v>5530</v>
+      </c>
+      <c r="E69" t="n">
+        <v>5020</v>
+      </c>
+      <c r="F69" t="n">
+        <v>5170</v>
+      </c>
+      <c r="G69" t="n">
+        <v>3610</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="n">
+        <v>5920</v>
+      </c>
+      <c r="J69" t="n">
+        <v>5250</v>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="n">
+        <v>3190</v>
+      </c>
+      <c r="M69" t="n">
+        <v>5510</v>
+      </c>
+      <c r="N69" t="n">
+        <v>5560</v>
+      </c>
+      <c r="O69" t="n">
+        <v>5090</v>
+      </c>
+      <c r="P69" t="n">
+        <v>5240</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>3180</v>
+      </c>
+      <c r="R69" t="n">
+        <v>5400</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5550</v>
+      </c>
+      <c r="T69" t="n">
+        <v>5030</v>
+      </c>
+      <c r="U69" t="n">
+        <v>5180</v>
+      </c>
+      <c r="V69" t="n">
+        <v>3130</v>
+      </c>
+      <c r="W69" t="n">
+        <v>5350</v>
+      </c>
+      <c r="X69" t="n">
+        <v>5500</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>5000</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>5150</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>3190</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>5540</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>5590</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>4900</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>5150</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>3180</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>5560</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>5550</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>5070</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>5220</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>3290</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>5610</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>5050</v>
+      </c>
+      <c r="AO69" t="inlineStr"/>
+      <c r="AP69" t="n">
+        <v>3460</v>
+      </c>
+      <c r="AQ69" t="inlineStr"/>
+      <c r="AR69" t="n">
+        <v>5850</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>5450</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>5550</v>
+      </c>
+      <c r="AU69" t="n">
+        <v>3140</v>
+      </c>
+      <c r="AV69" t="n">
+        <v>5560</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>5610</v>
+      </c>
+      <c r="AX69" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AY69" t="n">
+        <v>5100</v>
+      </c>
+      <c r="AZ69" t="n">
+        <v>3210</v>
+      </c>
+      <c r="BA69" t="n">
+        <v>5500</v>
+      </c>
+      <c r="BB69" t="n">
+        <v>5550</v>
+      </c>
+      <c r="BC69" t="n">
+        <v>5000</v>
+      </c>
+      <c r="BD69" t="n">
+        <v>5200</v>
+      </c>
+      <c r="BE69" t="n">
+        <v>3610</v>
+      </c>
+      <c r="BF69" t="inlineStr"/>
+      <c r="BG69" t="n">
+        <v>5900</v>
+      </c>
+      <c r="BH69" t="n">
+        <v>5350</v>
+      </c>
+      <c r="BI69" t="n">
+        <v>5450</v>
+      </c>
+      <c r="BJ69" t="n">
+        <v>3250</v>
+      </c>
+      <c r="BK69" t="n">
+        <v>5570</v>
+      </c>
+      <c r="BL69" t="n">
+        <v>5620</v>
+      </c>
+      <c r="BM69" t="n">
+        <v>5070</v>
+      </c>
+      <c r="BN69" t="n">
+        <v>5170</v>
+      </c>
+      <c r="BO69" t="n">
+        <v>3150</v>
+      </c>
+      <c r="BP69" t="n">
+        <v>5370</v>
+      </c>
+      <c r="BQ69" t="n">
+        <v>5520</v>
+      </c>
+      <c r="BR69" t="n">
+        <v>5000</v>
+      </c>
+      <c r="BS69" t="n">
+        <v>5150</v>
+      </c>
+      <c r="BT69" t="n">
+        <v>3250</v>
+      </c>
+      <c r="BU69" t="n">
+        <v>5570</v>
+      </c>
+      <c r="BV69" t="n">
+        <v>5540</v>
+      </c>
+      <c r="BW69" t="n">
+        <v>5030</v>
+      </c>
+      <c r="BX69" t="n">
+        <v>5180</v>
+      </c>
+      <c r="BY69" t="n">
+        <v>3230</v>
+      </c>
+      <c r="BZ69" t="inlineStr"/>
+      <c r="CA69" t="n">
+        <v>5610</v>
+      </c>
+      <c r="CB69" t="n">
+        <v>5020</v>
+      </c>
+      <c r="CC69" t="n">
+        <v>5270</v>
+      </c>
+      <c r="CD69" t="n">
+        <v>3160</v>
+      </c>
+      <c r="CE69" t="n">
+        <v>5500</v>
+      </c>
+      <c r="CF69" t="inlineStr"/>
+      <c r="CG69" t="n">
+        <v>5000</v>
+      </c>
+      <c r="CH69" t="inlineStr"/>
+      <c r="CI69" t="n">
+        <v>3040</v>
+      </c>
+      <c r="CJ69" t="n">
+        <v>4960</v>
+      </c>
+      <c r="CK69" t="n">
+        <v>4990</v>
+      </c>
+      <c r="CL69" t="n">
+        <v>4190</v>
+      </c>
+      <c r="CM69" t="n">
+        <v>4940</v>
+      </c>
+      <c r="CN69" t="n">
+        <v>3210</v>
+      </c>
+      <c r="CO69" t="n">
+        <v>5530</v>
+      </c>
+      <c r="CP69" t="n">
+        <v>5580</v>
+      </c>
+      <c r="CQ69" t="n">
+        <v>5050</v>
+      </c>
+      <c r="CR69" t="n">
+        <v>5100</v>
+      </c>
+      <c r="CS69" t="n">
+        <v>3560</v>
+      </c>
+      <c r="CT69" t="inlineStr"/>
+      <c r="CU69" t="n">
+        <v>5990</v>
+      </c>
+      <c r="CV69" t="n">
+        <v>5500</v>
+      </c>
+      <c r="CW69" t="n">
+        <v>5600</v>
+      </c>
+      <c r="CX69" t="n">
+        <v>3190</v>
+      </c>
+      <c r="CY69" t="n">
+        <v>5450</v>
+      </c>
+      <c r="CZ69" t="n">
+        <v>5500</v>
+      </c>
+      <c r="DA69" t="n">
+        <v>5010</v>
+      </c>
+      <c r="DB69" t="n">
+        <v>5160</v>
+      </c>
+      <c r="DC69" t="n">
+        <v>3460</v>
+      </c>
+      <c r="DD69" t="n">
+        <v>5870</v>
+      </c>
+      <c r="DE69" t="n">
+        <v>5920</v>
+      </c>
+      <c r="DF69" t="n">
+        <v>5600</v>
+      </c>
+      <c r="DG69" t="n">
+        <v>5700</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16962,7 +17598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DG67"/>
+  <dimension ref="A1:DG69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -33499,6 +34135,642 @@
         <v>5350</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>3160</v>
+      </c>
+      <c r="C68" t="n">
+        <v>5480</v>
+      </c>
+      <c r="D68" t="n">
+        <v>5530</v>
+      </c>
+      <c r="E68" t="n">
+        <v>5020</v>
+      </c>
+      <c r="F68" t="n">
+        <v>5170</v>
+      </c>
+      <c r="G68" t="n">
+        <v>3610</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="n">
+        <v>5990</v>
+      </c>
+      <c r="J68" t="n">
+        <v>5250</v>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="n">
+        <v>3190</v>
+      </c>
+      <c r="M68" t="n">
+        <v>5510</v>
+      </c>
+      <c r="N68" t="n">
+        <v>5560</v>
+      </c>
+      <c r="O68" t="n">
+        <v>5090</v>
+      </c>
+      <c r="P68" t="n">
+        <v>5240</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>3180</v>
+      </c>
+      <c r="R68" t="n">
+        <v>5500</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5550</v>
+      </c>
+      <c r="T68" t="n">
+        <v>5030</v>
+      </c>
+      <c r="U68" t="n">
+        <v>5180</v>
+      </c>
+      <c r="V68" t="n">
+        <v>3460</v>
+      </c>
+      <c r="W68" t="inlineStr"/>
+      <c r="X68" t="n">
+        <v>5850</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>5450</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>5550</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>3140</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>5560</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>5610</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>5100</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>3130</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>5450</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>5500</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>5150</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>3180</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>5560</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>5550</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>5070</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>5220</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>3190</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>5540</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>5590</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>4900</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>5150</v>
+      </c>
+      <c r="AU68" t="n">
+        <v>3290</v>
+      </c>
+      <c r="AV68" t="inlineStr"/>
+      <c r="AW68" t="n">
+        <v>5610</v>
+      </c>
+      <c r="AX68" t="n">
+        <v>5050</v>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="n">
+        <v>3460</v>
+      </c>
+      <c r="BA68" t="n">
+        <v>5870</v>
+      </c>
+      <c r="BB68" t="n">
+        <v>5920</v>
+      </c>
+      <c r="BC68" t="n">
+        <v>5600</v>
+      </c>
+      <c r="BD68" t="n">
+        <v>5700</v>
+      </c>
+      <c r="BE68" t="n">
+        <v>3150</v>
+      </c>
+      <c r="BF68" t="n">
+        <v>5470</v>
+      </c>
+      <c r="BG68" t="n">
+        <v>5520</v>
+      </c>
+      <c r="BH68" t="n">
+        <v>5000</v>
+      </c>
+      <c r="BI68" t="n">
+        <v>5150</v>
+      </c>
+      <c r="BJ68" t="n">
+        <v>3250</v>
+      </c>
+      <c r="BK68" t="n">
+        <v>5570</v>
+      </c>
+      <c r="BL68" t="n">
+        <v>5540</v>
+      </c>
+      <c r="BM68" t="n">
+        <v>5030</v>
+      </c>
+      <c r="BN68" t="n">
+        <v>5180</v>
+      </c>
+      <c r="BO68" t="n">
+        <v>3230</v>
+      </c>
+      <c r="BP68" t="inlineStr"/>
+      <c r="BQ68" t="n">
+        <v>5610</v>
+      </c>
+      <c r="BR68" t="n">
+        <v>5020</v>
+      </c>
+      <c r="BS68" t="n">
+        <v>5270</v>
+      </c>
+      <c r="BT68" t="n">
+        <v>3160</v>
+      </c>
+      <c r="BU68" t="n">
+        <v>5500</v>
+      </c>
+      <c r="BV68" t="inlineStr"/>
+      <c r="BW68" t="n">
+        <v>5000</v>
+      </c>
+      <c r="BX68" t="inlineStr"/>
+      <c r="BY68" t="n">
+        <v>3560</v>
+      </c>
+      <c r="BZ68" t="inlineStr"/>
+      <c r="CA68" t="n">
+        <v>5990</v>
+      </c>
+      <c r="CB68" t="n">
+        <v>5500</v>
+      </c>
+      <c r="CC68" t="n">
+        <v>5600</v>
+      </c>
+      <c r="CD68" t="n">
+        <v>3040</v>
+      </c>
+      <c r="CE68" t="n">
+        <v>4960</v>
+      </c>
+      <c r="CF68" t="n">
+        <v>4990</v>
+      </c>
+      <c r="CG68" t="n">
+        <v>4190</v>
+      </c>
+      <c r="CH68" t="n">
+        <v>4940</v>
+      </c>
+      <c r="CI68" t="n">
+        <v>3610</v>
+      </c>
+      <c r="CJ68" t="inlineStr"/>
+      <c r="CK68" t="n">
+        <v>5900</v>
+      </c>
+      <c r="CL68" t="n">
+        <v>5350</v>
+      </c>
+      <c r="CM68" t="n">
+        <v>5450</v>
+      </c>
+      <c r="CN68" t="n">
+        <v>3210</v>
+      </c>
+      <c r="CO68" t="n">
+        <v>5500</v>
+      </c>
+      <c r="CP68" t="n">
+        <v>5550</v>
+      </c>
+      <c r="CQ68" t="n">
+        <v>5000</v>
+      </c>
+      <c r="CR68" t="n">
+        <v>5200</v>
+      </c>
+      <c r="CS68" t="n">
+        <v>3250</v>
+      </c>
+      <c r="CT68" t="n">
+        <v>5570</v>
+      </c>
+      <c r="CU68" t="n">
+        <v>5620</v>
+      </c>
+      <c r="CV68" t="n">
+        <v>5070</v>
+      </c>
+      <c r="CW68" t="n">
+        <v>5170</v>
+      </c>
+      <c r="CX68" t="n">
+        <v>3190</v>
+      </c>
+      <c r="CY68" t="n">
+        <v>5450</v>
+      </c>
+      <c r="CZ68" t="n">
+        <v>5500</v>
+      </c>
+      <c r="DA68" t="n">
+        <v>5010</v>
+      </c>
+      <c r="DB68" t="n">
+        <v>5160</v>
+      </c>
+      <c r="DC68" t="n">
+        <v>3210</v>
+      </c>
+      <c r="DD68" t="n">
+        <v>5530</v>
+      </c>
+      <c r="DE68" t="n">
+        <v>5580</v>
+      </c>
+      <c r="DF68" t="n">
+        <v>5000</v>
+      </c>
+      <c r="DG68" t="n">
+        <v>5100</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>3160</v>
+      </c>
+      <c r="C69" t="n">
+        <v>5480</v>
+      </c>
+      <c r="D69" t="n">
+        <v>5530</v>
+      </c>
+      <c r="E69" t="n">
+        <v>5020</v>
+      </c>
+      <c r="F69" t="n">
+        <v>5170</v>
+      </c>
+      <c r="G69" t="n">
+        <v>3610</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="n">
+        <v>5920</v>
+      </c>
+      <c r="J69" t="n">
+        <v>5250</v>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="n">
+        <v>3190</v>
+      </c>
+      <c r="M69" t="n">
+        <v>5510</v>
+      </c>
+      <c r="N69" t="n">
+        <v>5560</v>
+      </c>
+      <c r="O69" t="n">
+        <v>5090</v>
+      </c>
+      <c r="P69" t="n">
+        <v>5240</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>3180</v>
+      </c>
+      <c r="R69" t="n">
+        <v>5400</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5550</v>
+      </c>
+      <c r="T69" t="n">
+        <v>5030</v>
+      </c>
+      <c r="U69" t="n">
+        <v>5180</v>
+      </c>
+      <c r="V69" t="n">
+        <v>3460</v>
+      </c>
+      <c r="W69" t="inlineStr"/>
+      <c r="X69" t="n">
+        <v>5850</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>5450</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>5550</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>3140</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>5560</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>5610</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>5100</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>3130</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>5350</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>5500</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>5150</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>3180</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>5560</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>5550</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>5070</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>5220</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>3190</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>5540</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>5590</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>4900</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>5150</v>
+      </c>
+      <c r="AU69" t="n">
+        <v>3290</v>
+      </c>
+      <c r="AV69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>5610</v>
+      </c>
+      <c r="AX69" t="n">
+        <v>5050</v>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="n">
+        <v>3460</v>
+      </c>
+      <c r="BA69" t="n">
+        <v>5870</v>
+      </c>
+      <c r="BB69" t="n">
+        <v>5920</v>
+      </c>
+      <c r="BC69" t="n">
+        <v>5600</v>
+      </c>
+      <c r="BD69" t="n">
+        <v>5700</v>
+      </c>
+      <c r="BE69" t="n">
+        <v>3150</v>
+      </c>
+      <c r="BF69" t="n">
+        <v>5370</v>
+      </c>
+      <c r="BG69" t="n">
+        <v>5520</v>
+      </c>
+      <c r="BH69" t="n">
+        <v>5000</v>
+      </c>
+      <c r="BI69" t="n">
+        <v>5150</v>
+      </c>
+      <c r="BJ69" t="n">
+        <v>3250</v>
+      </c>
+      <c r="BK69" t="n">
+        <v>5570</v>
+      </c>
+      <c r="BL69" t="n">
+        <v>5540</v>
+      </c>
+      <c r="BM69" t="n">
+        <v>5030</v>
+      </c>
+      <c r="BN69" t="n">
+        <v>5180</v>
+      </c>
+      <c r="BO69" t="n">
+        <v>3230</v>
+      </c>
+      <c r="BP69" t="inlineStr"/>
+      <c r="BQ69" t="n">
+        <v>5610</v>
+      </c>
+      <c r="BR69" t="n">
+        <v>5020</v>
+      </c>
+      <c r="BS69" t="n">
+        <v>5270</v>
+      </c>
+      <c r="BT69" t="n">
+        <v>3160</v>
+      </c>
+      <c r="BU69" t="n">
+        <v>5500</v>
+      </c>
+      <c r="BV69" t="inlineStr"/>
+      <c r="BW69" t="n">
+        <v>5000</v>
+      </c>
+      <c r="BX69" t="inlineStr"/>
+      <c r="BY69" t="n">
+        <v>3560</v>
+      </c>
+      <c r="BZ69" t="inlineStr"/>
+      <c r="CA69" t="n">
+        <v>5990</v>
+      </c>
+      <c r="CB69" t="n">
+        <v>5500</v>
+      </c>
+      <c r="CC69" t="n">
+        <v>5600</v>
+      </c>
+      <c r="CD69" t="n">
+        <v>3040</v>
+      </c>
+      <c r="CE69" t="n">
+        <v>4960</v>
+      </c>
+      <c r="CF69" t="n">
+        <v>4990</v>
+      </c>
+      <c r="CG69" t="n">
+        <v>4190</v>
+      </c>
+      <c r="CH69" t="n">
+        <v>4940</v>
+      </c>
+      <c r="CI69" t="n">
+        <v>3610</v>
+      </c>
+      <c r="CJ69" t="inlineStr"/>
+      <c r="CK69" t="n">
+        <v>5900</v>
+      </c>
+      <c r="CL69" t="n">
+        <v>5350</v>
+      </c>
+      <c r="CM69" t="n">
+        <v>5450</v>
+      </c>
+      <c r="CN69" t="n">
+        <v>3210</v>
+      </c>
+      <c r="CO69" t="n">
+        <v>5500</v>
+      </c>
+      <c r="CP69" t="n">
+        <v>5550</v>
+      </c>
+      <c r="CQ69" t="n">
+        <v>5000</v>
+      </c>
+      <c r="CR69" t="n">
+        <v>5200</v>
+      </c>
+      <c r="CS69" t="n">
+        <v>3250</v>
+      </c>
+      <c r="CT69" t="n">
+        <v>5570</v>
+      </c>
+      <c r="CU69" t="n">
+        <v>5620</v>
+      </c>
+      <c r="CV69" t="n">
+        <v>5070</v>
+      </c>
+      <c r="CW69" t="n">
+        <v>5170</v>
+      </c>
+      <c r="CX69" t="n">
+        <v>3190</v>
+      </c>
+      <c r="CY69" t="n">
+        <v>5450</v>
+      </c>
+      <c r="CZ69" t="n">
+        <v>5500</v>
+      </c>
+      <c r="DA69" t="n">
+        <v>5010</v>
+      </c>
+      <c r="DB69" t="n">
+        <v>5160</v>
+      </c>
+      <c r="DC69" t="n">
+        <v>3210</v>
+      </c>
+      <c r="DD69" t="n">
+        <v>5530</v>
+      </c>
+      <c r="DE69" t="n">
+        <v>5580</v>
+      </c>
+      <c r="DF69" t="n">
+        <v>5050</v>
+      </c>
+      <c r="DG69" t="n">
+        <v>5100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
